--- a/mosip_master/xlsx/dynamic_field.xlsx
+++ b/mosip_master/xlsx/dynamic_field.xlsx
@@ -1,33 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahesh.Binayak\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6720" tabRatio="500"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$102</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="116">
   <si>
     <t>id</t>
   </si>
@@ -210,13 +213,6 @@
 	{
 		"code": "105",
 		"value": "Legally Separated"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "106",
-		"value": "Annulled"
 	}</t>
   </si>
   <si>
@@ -667,39 +663,417 @@
   </si>
   <si>
     <t>{"value":"عربي","code":"ara"}</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ {
+  "code": "CTZ",
+  "value": "No aplicable"
+ }</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {
+  "code": "FR",
+  "value": "Non-Citizen - Foreigner"
+ }</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {
+  "code": "NFR",
+  "value": "Non-Citizen- Migrant"
+ }</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {
+  "code": "NFR",
+  "value": "Non-Citizen- Refugee"
+ }</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {
+  "code": "NFR",
+  "value": "Non-Citizen- Foreign Worker"
+ }</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
+    <numFmt numFmtId="181" formatCode="h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -722,11 +1096,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -734,19 +1350,75 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="47" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -795,7 +1467,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -830,7 +1502,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1004,32 +1676,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I103"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:M108"/>
+  <sheetFormatPr defaultColWidth="8.57142857142857" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="21.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="32.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="15.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="14.2857142857143" customWidth="1"/>
+    <col min="8" max="8" width="11.5714285714286" customWidth="1"/>
+    <col min="9" max="9" width="15.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1725,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" ht="75" hidden="1" spans="1:9">
       <c r="A2">
         <v>10001</v>
       </c>
@@ -1088,7 +1755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" ht="75" hidden="1" spans="1:9">
       <c r="A3">
         <v>10002</v>
       </c>
@@ -1118,7 +1785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" ht="75" hidden="1" spans="1:9">
       <c r="A4">
         <v>10003</v>
       </c>
@@ -1148,7 +1815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" ht="75" hidden="1" spans="1:9">
       <c r="A5">
         <v>10004</v>
       </c>
@@ -1178,7 +1845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" ht="75" hidden="1" spans="1:9">
       <c r="A6">
         <v>10005</v>
       </c>
@@ -1208,7 +1875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" ht="75" hidden="1" spans="1:9">
       <c r="A7">
         <v>10006</v>
       </c>
@@ -1238,7 +1905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" ht="75" hidden="1" spans="1:9">
       <c r="A8">
         <v>10007</v>
       </c>
@@ -1268,7 +1935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" ht="75" hidden="1" spans="1:9">
       <c r="A9">
         <v>10008</v>
       </c>
@@ -1298,7 +1965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" ht="75" hidden="1" spans="1:9">
       <c r="A10">
         <v>10009</v>
       </c>
@@ -1328,7 +1995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" ht="75" hidden="1" spans="1:9">
       <c r="A11">
         <v>10010</v>
       </c>
@@ -1358,7 +2025,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" ht="75" hidden="1" spans="1:9">
       <c r="A12">
         <v>10011</v>
       </c>
@@ -1388,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" ht="75" hidden="1" spans="1:9">
       <c r="A13">
         <v>10012</v>
       </c>
@@ -1418,7 +2085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" ht="75" hidden="1" spans="1:9">
       <c r="A14">
         <v>10013</v>
       </c>
@@ -1448,7 +2115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" ht="75" hidden="1" spans="1:9">
       <c r="A15">
         <v>10014</v>
       </c>
@@ -1478,7 +2145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" ht="75" spans="1:9">
       <c r="A16">
         <v>10015</v>
       </c>
@@ -1508,7 +2175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" ht="75" spans="1:9">
       <c r="A17">
         <v>10016</v>
       </c>
@@ -1538,7 +2205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" ht="75" spans="1:9">
       <c r="A18">
         <v>10017</v>
       </c>
@@ -1568,7 +2235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" ht="75" spans="1:9">
       <c r="A19">
         <v>10018</v>
       </c>
@@ -1598,7 +2265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" ht="75" spans="1:9">
       <c r="A20">
         <v>10019</v>
       </c>
@@ -1628,9 +2295,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" ht="75" spans="1:9">
       <c r="A21">
-        <v>10020</v>
+        <v>10021</v>
       </c>
       <c r="B21" t="s">
         <v>29</v>
@@ -1648,7 +2315,7 @@
         <v>13</v>
       </c>
       <c r="G21" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" ref="G21:G64" si="0">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H21" t="s">
@@ -1658,27 +2325,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" ht="75" hidden="1" spans="1:9">
       <c r="A22">
-        <v>10021</v>
+        <v>10022</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H22" t="s">
@@ -1688,15 +2355,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" ht="75" hidden="1" spans="1:9">
       <c r="A23">
-        <v>10022</v>
+        <v>10023</v>
       </c>
       <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
         <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1708,7 +2375,7 @@
         <v>13</v>
       </c>
       <c r="G23" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H23" t="s">
@@ -1718,27 +2385,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" ht="75" hidden="1" spans="1:9">
       <c r="A24">
-        <v>10023</v>
+        <v>10024</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H24" t="s">
@@ -1748,15 +2415,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" ht="90" hidden="1" spans="1:9">
       <c r="A25">
-        <v>10024</v>
+        <v>10025</v>
       </c>
       <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
         <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>43</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1768,7 +2435,7 @@
         <v>13</v>
       </c>
       <c r="G25" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H25" t="s">
@@ -1778,15 +2445,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="26" ht="90" hidden="1" spans="1:9">
       <c r="A26">
-        <v>10025</v>
+        <v>10026</v>
       </c>
       <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
         <v>42</v>
-      </c>
-      <c r="C26" t="s">
-        <v>43</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1798,7 +2465,7 @@
         <v>13</v>
       </c>
       <c r="G26" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H26" t="s">
@@ -1808,27 +2475,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="27" ht="75" hidden="1" spans="1:9">
       <c r="A27">
-        <v>10026</v>
+        <v>10027</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H27" t="s">
@@ -1838,15 +2505,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="28" ht="75" hidden="1" spans="1:9">
       <c r="A28">
-        <v>10027</v>
+        <v>10028</v>
       </c>
       <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
         <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1858,7 +2525,7 @@
         <v>13</v>
       </c>
       <c r="G28" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H28" t="s">
@@ -1868,15 +2535,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="29" ht="75" hidden="1" spans="1:9">
       <c r="A29">
-        <v>10028</v>
+        <v>10029</v>
       </c>
       <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
         <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>48</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -1888,7 +2555,7 @@
         <v>13</v>
       </c>
       <c r="G29" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H29" t="s">
@@ -1898,27 +2565,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" ht="75" spans="1:9">
       <c r="A30">
-        <v>10029</v>
+        <v>10030</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H30" t="s">
@@ -1928,15 +2595,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" ht="75" spans="1:9">
       <c r="A31">
-        <v>10030</v>
+        <v>10031</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -1948,7 +2615,7 @@
         <v>13</v>
       </c>
       <c r="G31" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H31" t="s">
@@ -1958,45 +2625,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>10031</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" t="s">
+    <row r="32" ht="30" hidden="1" spans="1:9">
+      <c r="A32" s="2">
+        <v>10310</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" ht="30" hidden="1" spans="1:9">
+      <c r="A33" s="2">
+        <v>10313</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>10310</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
@@ -2008,7 +2675,7 @@
         <v>13</v>
       </c>
       <c r="G33" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -2018,45 +2685,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" ht="30" hidden="1" spans="1:9">
       <c r="A34" s="2">
-        <v>10313</v>
+        <v>10317</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" ht="30" hidden="1" spans="1:9">
+      <c r="A35" s="2">
+        <v>10319</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>10317</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>11</v>
@@ -2065,10 +2732,10 @@
         <v>57</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G35" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
@@ -2078,39 +2745,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>10319</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="2" t="s">
+    <row r="36" ht="75" hidden="1" spans="1:9">
+      <c r="A36">
+        <v>10063</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="G36" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" ht="75" hidden="1" spans="1:9">
       <c r="A37">
-        <v>10063</v>
+        <v>10064</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -2122,13 +2789,13 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G37" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H37" t="s">
@@ -2138,9 +2805,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" ht="75" hidden="1" spans="1:9">
       <c r="A38">
-        <v>10064</v>
+        <v>10065</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -2152,13 +2819,13 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G38" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H38" t="s">
@@ -2168,9 +2835,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" ht="75" hidden="1" spans="1:9">
       <c r="A39">
-        <v>10065</v>
+        <v>10066</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -2182,13 +2849,13 @@
         <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G39" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H39" t="s">
@@ -2198,9 +2865,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" ht="75" hidden="1" spans="1:9">
       <c r="A40">
-        <v>10066</v>
+        <v>10067</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -2212,13 +2879,13 @@
         <v>11</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G40" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H40" t="s">
@@ -2228,9 +2895,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" ht="75" hidden="1" spans="1:9">
       <c r="A41">
-        <v>10067</v>
+        <v>10068</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -2242,13 +2909,13 @@
         <v>11</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G41" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H41" t="s">
@@ -2258,9 +2925,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" ht="75" hidden="1" spans="1:9">
       <c r="A42">
-        <v>10068</v>
+        <v>10069</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -2272,13 +2939,13 @@
         <v>11</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G42" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H42" t="s">
@@ -2288,9 +2955,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" ht="75" hidden="1" spans="1:9">
       <c r="A43">
-        <v>10069</v>
+        <v>10070</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -2302,13 +2969,13 @@
         <v>11</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G43" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H43" t="s">
@@ -2318,9 +2985,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="44" ht="75" hidden="1" spans="1:9">
       <c r="A44">
-        <v>10070</v>
+        <v>10071</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -2332,13 +2999,13 @@
         <v>11</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G44" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H44" t="s">
@@ -2348,9 +3015,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" ht="75" hidden="1" spans="1:9">
       <c r="A45">
-        <v>10071</v>
+        <v>10072</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -2362,13 +3029,13 @@
         <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G45" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H45" t="s">
@@ -2378,9 +3045,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="46" ht="75" hidden="1" spans="1:9">
       <c r="A46">
-        <v>10072</v>
+        <v>10073</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -2392,13 +3059,13 @@
         <v>11</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G46" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H46" t="s">
@@ -2408,9 +3075,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" ht="75" hidden="1" spans="1:9">
       <c r="A47">
-        <v>10073</v>
+        <v>10074</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -2422,13 +3089,13 @@
         <v>11</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G47" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H47" t="s">
@@ -2438,9 +3105,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" ht="75" hidden="1" spans="1:9">
       <c r="A48">
-        <v>10074</v>
+        <v>10075</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -2452,13 +3119,13 @@
         <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G48" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H48" t="s">
@@ -2468,9 +3135,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" ht="75" hidden="1" spans="1:9">
       <c r="A49">
-        <v>10075</v>
+        <v>10076</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -2485,10 +3152,10 @@
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G49" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H49" t="s">
@@ -2498,15 +3165,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" ht="75" hidden="1" spans="1:9">
       <c r="A50">
-        <v>10076</v>
+        <v>10077</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2515,10 +3182,10 @@
         <v>62</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G50" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H50" t="s">
@@ -2528,9 +3195,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" ht="75" hidden="1" spans="1:9">
       <c r="A51">
-        <v>10077</v>
+        <v>10078</v>
       </c>
       <c r="B51" t="s">
         <v>29</v>
@@ -2545,10 +3212,10 @@
         <v>63</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G51" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H51" t="s">
@@ -2558,9 +3225,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" ht="75" hidden="1" spans="1:9">
       <c r="A52">
-        <v>10078</v>
+        <v>10079</v>
       </c>
       <c r="B52" t="s">
         <v>29</v>
@@ -2575,10 +3242,10 @@
         <v>64</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G52" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H52" t="s">
@@ -2588,9 +3255,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" ht="75" hidden="1" spans="1:9">
       <c r="A53">
-        <v>10079</v>
+        <v>10080</v>
       </c>
       <c r="B53" t="s">
         <v>29</v>
@@ -2605,10 +3272,10 @@
         <v>65</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G53" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H53" t="s">
@@ -2618,9 +3285,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" ht="75" hidden="1" spans="1:9">
       <c r="A54">
-        <v>10080</v>
+        <v>10081</v>
       </c>
       <c r="B54" t="s">
         <v>29</v>
@@ -2635,10 +3302,10 @@
         <v>66</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G54" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H54" t="s">
@@ -2648,9 +3315,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="55" ht="75" hidden="1" spans="1:9">
       <c r="A55">
-        <v>10081</v>
+        <v>10082</v>
       </c>
       <c r="B55" t="s">
         <v>29</v>
@@ -2665,10 +3332,10 @@
         <v>67</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G55" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H55" t="s">
@@ -2678,9 +3345,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" ht="75" hidden="1" spans="1:9">
       <c r="A56">
-        <v>10082</v>
+        <v>10083</v>
       </c>
       <c r="B56" t="s">
         <v>29</v>
@@ -2695,10 +3362,10 @@
         <v>68</v>
       </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G56" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H56" t="s">
@@ -2708,15 +3375,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" ht="75" hidden="1" spans="1:9">
       <c r="A57">
-        <v>10083</v>
+        <v>10084</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2725,10 +3392,10 @@
         <v>69</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G57" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H57" t="s">
@@ -2738,15 +3405,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="58" ht="75" hidden="1" spans="1:9">
       <c r="A58">
-        <v>10084</v>
+        <v>10085</v>
       </c>
       <c r="B58" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" t="s">
         <v>38</v>
-      </c>
-      <c r="C58" t="s">
-        <v>39</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -2755,10 +3422,10 @@
         <v>70</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G58" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H58" t="s">
@@ -2768,15 +3435,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="59" ht="75" hidden="1" spans="1:9">
       <c r="A59">
-        <v>10085</v>
+        <v>10086</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2785,10 +3452,10 @@
         <v>71</v>
       </c>
       <c r="F59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G59" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H59" t="s">
@@ -2798,15 +3465,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="60" ht="90" hidden="1" spans="1:9">
       <c r="A60">
-        <v>10086</v>
+        <v>10087</v>
       </c>
       <c r="B60" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" t="s">
         <v>42</v>
-      </c>
-      <c r="C60" t="s">
-        <v>43</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2815,10 +3482,10 @@
         <v>72</v>
       </c>
       <c r="F60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G60" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H60" t="s">
@@ -2828,15 +3495,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" ht="90" hidden="1" spans="1:9">
       <c r="A61">
-        <v>10087</v>
+        <v>10088</v>
       </c>
       <c r="B61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" t="s">
         <v>42</v>
-      </c>
-      <c r="C61" t="s">
-        <v>43</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -2845,10 +3512,10 @@
         <v>73</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G61" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H61" t="s">
@@ -2858,15 +3525,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="62" ht="75" hidden="1" spans="1:9">
       <c r="A62">
-        <v>10088</v>
+        <v>10089</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C62" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2875,10 +3542,10 @@
         <v>74</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G62" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H62" t="s">
@@ -2888,15 +3555,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="63" ht="75" hidden="1" spans="1:9">
       <c r="A63">
-        <v>10089</v>
+        <v>10090</v>
       </c>
       <c r="B63" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" t="s">
         <v>47</v>
-      </c>
-      <c r="C63" t="s">
-        <v>48</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -2905,10 +3572,10 @@
         <v>75</v>
       </c>
       <c r="F63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G63" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H63" t="s">
@@ -2918,15 +3585,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" ht="75" hidden="1" spans="1:9">
       <c r="A64">
-        <v>10090</v>
+        <v>10091</v>
       </c>
       <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" t="s">
         <v>47</v>
-      </c>
-      <c r="C64" t="s">
-        <v>48</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -2935,10 +3602,10 @@
         <v>76</v>
       </c>
       <c r="F64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G64" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H64" t="s">
@@ -2948,15 +3615,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="65" ht="75" hidden="1" spans="1:9">
       <c r="A65">
-        <v>10091</v>
+        <v>10092</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C65" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -2965,10 +3632,10 @@
         <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G65" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" ref="G65:G102" si="1">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H65" t="s">
@@ -2978,15 +3645,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="66" ht="75" hidden="1" spans="1:9">
       <c r="A66">
-        <v>10092</v>
+        <v>10093</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C66" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -2995,10 +3662,10 @@
         <v>78</v>
       </c>
       <c r="F66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G66" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H66" t="s">
@@ -3008,15 +3675,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" ht="75" hidden="1" spans="1:9">
       <c r="A67">
-        <v>10093</v>
+        <v>10094</v>
       </c>
       <c r="B67" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -3025,10 +3692,10 @@
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G67" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H67" t="s">
@@ -3038,9 +3705,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" ht="75" hidden="1" spans="1:9">
       <c r="A68">
-        <v>10094</v>
+        <v>10095</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
@@ -3052,13 +3719,13 @@
         <v>11</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" t="s">
         <v>80</v>
       </c>
-      <c r="F68" t="s">
-        <v>81</v>
-      </c>
       <c r="G68" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H68" t="s">
@@ -3068,9 +3735,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="69" ht="75" hidden="1" spans="1:9">
       <c r="A69">
-        <v>10095</v>
+        <v>10096</v>
       </c>
       <c r="B69" t="s">
         <v>9</v>
@@ -3085,10 +3752,10 @@
         <v>82</v>
       </c>
       <c r="F69" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G69" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H69" t="s">
@@ -3098,9 +3765,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="70" ht="75" hidden="1" spans="1:9">
       <c r="A70">
-        <v>10096</v>
+        <v>10097</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -3115,10 +3782,10 @@
         <v>83</v>
       </c>
       <c r="F70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G70" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H70" t="s">
@@ -3128,9 +3795,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="71" ht="75" hidden="1" spans="1:9">
       <c r="A71">
-        <v>10097</v>
+        <v>10098</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -3145,10 +3812,10 @@
         <v>84</v>
       </c>
       <c r="F71" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G71" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H71" t="s">
@@ -3158,9 +3825,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="72" ht="75" hidden="1" spans="1:9">
       <c r="A72">
-        <v>10098</v>
+        <v>10099</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
@@ -3175,10 +3842,10 @@
         <v>85</v>
       </c>
       <c r="F72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G72" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H72" t="s">
@@ -3188,9 +3855,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="73" ht="75" hidden="1" spans="1:9">
       <c r="A73">
-        <v>10099</v>
+        <v>10100</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
@@ -3202,13 +3869,13 @@
         <v>11</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="F73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G73" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H73" t="s">
@@ -3218,9 +3885,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="74" ht="75" hidden="1" spans="1:9">
       <c r="A74">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
@@ -3232,13 +3899,13 @@
         <v>11</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G74" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H74" t="s">
@@ -3248,9 +3915,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="75" ht="75" hidden="1" spans="1:9">
       <c r="A75">
-        <v>10101</v>
+        <v>10102</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
@@ -3262,13 +3929,13 @@
         <v>11</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G75" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H75" t="s">
@@ -3278,9 +3945,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="76" ht="75" hidden="1" spans="1:9">
       <c r="A76">
-        <v>10102</v>
+        <v>10103</v>
       </c>
       <c r="B76" t="s">
         <v>9</v>
@@ -3292,13 +3959,13 @@
         <v>11</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="F76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G76" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H76" t="s">
@@ -3308,9 +3975,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="77" ht="75" hidden="1" spans="1:9">
       <c r="A77">
-        <v>10103</v>
+        <v>10104</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
@@ -3322,13 +3989,13 @@
         <v>11</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G77" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H77" t="s">
@@ -3338,9 +4005,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" ht="75" hidden="1" spans="1:9">
       <c r="A78">
-        <v>10104</v>
+        <v>10105</v>
       </c>
       <c r="B78" t="s">
         <v>9</v>
@@ -3352,13 +4019,13 @@
         <v>11</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="F78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G78" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H78" t="s">
@@ -3368,9 +4035,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" ht="75" hidden="1" spans="1:9">
       <c r="A79">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
@@ -3385,10 +4052,10 @@
         <v>88</v>
       </c>
       <c r="F79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G79" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H79" t="s">
@@ -3398,9 +4065,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="80" ht="75" hidden="1" spans="1:9">
       <c r="A80">
-        <v>10106</v>
+        <v>10107</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
@@ -3415,10 +4082,10 @@
         <v>89</v>
       </c>
       <c r="F80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G80" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H80" t="s">
@@ -3428,15 +4095,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" ht="90" hidden="1" spans="1:9">
       <c r="A81">
-        <v>10107</v>
+        <v>10108</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C81" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -3445,10 +4112,10 @@
         <v>90</v>
       </c>
       <c r="F81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G81" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H81" t="s">
@@ -3458,9 +4125,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="82" ht="75" hidden="1" spans="1:9">
       <c r="A82">
-        <v>10108</v>
+        <v>10109</v>
       </c>
       <c r="B82" t="s">
         <v>29</v>
@@ -3475,10 +4142,10 @@
         <v>91</v>
       </c>
       <c r="F82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G82" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H82" t="s">
@@ -3488,9 +4155,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="83" ht="75" hidden="1" spans="1:9">
       <c r="A83">
-        <v>10109</v>
+        <v>10110</v>
       </c>
       <c r="B83" t="s">
         <v>29</v>
@@ -3505,10 +4172,10 @@
         <v>92</v>
       </c>
       <c r="F83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G83" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H83" t="s">
@@ -3518,9 +4185,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="84" ht="75" hidden="1" spans="1:9">
       <c r="A84">
-        <v>10110</v>
+        <v>10111</v>
       </c>
       <c r="B84" t="s">
         <v>29</v>
@@ -3535,10 +4202,10 @@
         <v>93</v>
       </c>
       <c r="F84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G84" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H84" t="s">
@@ -3548,9 +4215,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="85" ht="90" hidden="1" spans="1:9">
       <c r="A85">
-        <v>10111</v>
+        <v>10112</v>
       </c>
       <c r="B85" t="s">
         <v>29</v>
@@ -3565,10 +4232,10 @@
         <v>94</v>
       </c>
       <c r="F85" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G85" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H85" t="s">
@@ -3578,9 +4245,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="86" ht="75" hidden="1" spans="1:9">
       <c r="A86">
-        <v>10112</v>
+        <v>10113</v>
       </c>
       <c r="B86" t="s">
         <v>29</v>
@@ -3595,10 +4262,10 @@
         <v>95</v>
       </c>
       <c r="F86" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G86" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H86" t="s">
@@ -3608,9 +4275,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="87" ht="75" hidden="1" spans="1:9">
       <c r="A87">
-        <v>10113</v>
+        <v>10114</v>
       </c>
       <c r="B87" t="s">
         <v>29</v>
@@ -3625,10 +4292,10 @@
         <v>96</v>
       </c>
       <c r="F87" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G87" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H87" t="s">
@@ -3638,15 +4305,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="88" ht="75" hidden="1" spans="1:9">
       <c r="A88">
-        <v>10114</v>
+        <v>10115</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
@@ -3655,10 +4322,10 @@
         <v>97</v>
       </c>
       <c r="F88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G88" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H88" t="s">
@@ -3668,15 +4335,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="89" ht="75" hidden="1" spans="1:9">
       <c r="A89">
-        <v>10115</v>
+        <v>10116</v>
       </c>
       <c r="B89" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89" t="s">
         <v>38</v>
-      </c>
-      <c r="C89" t="s">
-        <v>39</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -3685,10 +4352,10 @@
         <v>98</v>
       </c>
       <c r="F89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G89" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H89" t="s">
@@ -3698,15 +4365,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="90" ht="75" hidden="1" spans="1:9">
       <c r="A90">
-        <v>10116</v>
+        <v>10117</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C90" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
@@ -3715,10 +4382,10 @@
         <v>99</v>
       </c>
       <c r="F90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G90" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H90" t="s">
@@ -3728,15 +4395,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="91" ht="75" hidden="1" spans="1:9">
       <c r="A91">
-        <v>10117</v>
+        <v>10118</v>
       </c>
       <c r="B91" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" t="s">
         <v>42</v>
-      </c>
-      <c r="C91" t="s">
-        <v>43</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
@@ -3745,10 +4412,10 @@
         <v>100</v>
       </c>
       <c r="F91" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G91" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H91" t="s">
@@ -3758,15 +4425,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="92" ht="75" hidden="1" spans="1:9">
       <c r="A92">
-        <v>10118</v>
+        <v>10119</v>
       </c>
       <c r="B92" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" t="s">
         <v>42</v>
-      </c>
-      <c r="C92" t="s">
-        <v>43</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
@@ -3775,10 +4442,10 @@
         <v>101</v>
       </c>
       <c r="F92" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G92" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H92" t="s">
@@ -3788,15 +4455,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" ht="75" hidden="1" spans="1:9">
       <c r="A93">
-        <v>10119</v>
+        <v>10120</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C93" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -3805,10 +4472,10 @@
         <v>102</v>
       </c>
       <c r="F93" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G93" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H93" t="s">
@@ -3818,15 +4485,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="94" ht="75" hidden="1" spans="1:9">
       <c r="A94">
-        <v>10120</v>
+        <v>10121</v>
       </c>
       <c r="B94" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" t="s">
         <v>47</v>
-      </c>
-      <c r="C94" t="s">
-        <v>48</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
@@ -3835,10 +4502,10 @@
         <v>103</v>
       </c>
       <c r="F94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G94" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H94" t="s">
@@ -3848,15 +4515,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="95" ht="75" hidden="1" spans="1:9">
       <c r="A95">
-        <v>10121</v>
+        <v>10122</v>
       </c>
       <c r="B95" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" t="s">
         <v>47</v>
-      </c>
-      <c r="C95" t="s">
-        <v>48</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
@@ -3865,10 +4532,10 @@
         <v>104</v>
       </c>
       <c r="F95" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G95" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H95" t="s">
@@ -3878,15 +4545,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="96" ht="75" hidden="1" spans="1:9">
       <c r="A96">
-        <v>10122</v>
+        <v>10123</v>
       </c>
       <c r="B96" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C96" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
@@ -3895,10 +4562,10 @@
         <v>105</v>
       </c>
       <c r="F96" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G96" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H96" t="s">
@@ -3908,15 +4575,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="97" ht="75" hidden="1" spans="1:9">
       <c r="A97">
-        <v>10123</v>
+        <v>10124</v>
       </c>
       <c r="B97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -3925,10 +4592,10 @@
         <v>106</v>
       </c>
       <c r="F97" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G97" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H97" t="s">
@@ -3938,57 +4605,54 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="98" ht="30" hidden="1" spans="1:9">
       <c r="A98">
-        <v>10124</v>
-      </c>
-      <c r="B98" t="s">
-        <v>52</v>
-      </c>
-      <c r="C98" t="s">
-        <v>52</v>
-      </c>
-      <c r="D98" t="s">
+        <v>10125</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F98" t="s">
-        <v>81</v>
+      <c r="F98" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G98" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H98" t="s">
-        <v>14</v>
-      </c>
-      <c r="I98" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" ht="30" hidden="1" spans="1:9">
       <c r="A99">
-        <v>10125</v>
+        <v>10126</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G99" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H99" s="2" t="s">
@@ -3998,78 +4662,78 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" ht="30" hidden="1" spans="1:9">
       <c r="A100">
-        <v>10126</v>
+        <v>10127</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G100" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" ht="30" hidden="1" spans="1:9">
+      <c r="A101">
+        <v>10128</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>10127</v>
-      </c>
-      <c r="B101" s="2" t="s">
+      <c r="F101" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G101" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" ht="30" hidden="1" spans="1:9">
+      <c r="A102">
+        <v>10129</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G101" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>10128</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G102" s="3" t="b">
-        <f>TRUE()</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H102" s="2" t="s">
@@ -4079,36 +4743,221 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>10129</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G103" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>15</v>
-      </c>
+    <row r="103" ht="75" spans="1:13">
+      <c r="A103" s="4">
+        <v>13332</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+    </row>
+    <row r="104" ht="60" spans="1:13">
+      <c r="A104" s="4">
+        <v>13333</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+    </row>
+    <row r="105" ht="60" spans="1:13">
+      <c r="A105" s="4">
+        <v>13334</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+    </row>
+    <row r="106" ht="60" spans="1:13">
+      <c r="A106" s="4">
+        <v>13335</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+    </row>
+    <row r="107" ht="60" spans="1:13">
+      <c r="A107" s="4">
+        <v>13336</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+    </row>
+    <row r="108" ht="75" spans="1:13">
+      <c r="A108" s="4">
+        <v>13337</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I108" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I103"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I102" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Marital Status"/>
+        <filter val="residenceStatus"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="eng"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>